--- a/stage4_competency_graph/output/03_三级能力与课程知识技能支撑关系.xlsx
+++ b/stage4_competency_graph/output/03_三级能力与课程知识技能支撑关系.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只在问题记录和修正规则已给定时支持UPDATE实施；不涵盖问题识别、清洗规则设计及清洗结果验证。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q7" t="b">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只支持给定清洗条件的记录定位；不证明完整清洗流程、异常判断及前后质量验证已安排。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q8" t="b">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>第5页明确主键作用及语法；仅在关系表标识方案已确定时支持实现表达，不能把约束SQL实现等同完整模式设计。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q19" t="b">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>第5页明确外键作用及语法；仅在参照关系方案已确定时支持实现，不替代实体关系识别与完整结构设计。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q20" t="b">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只支持选定索引方案的创建实施，不证明能根据查询需求选择索引或验证调整收益。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q23" t="b">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只支持既定方案的索引添加实施；索引选择、负面影响分析及迭代调整仍需其他依据。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q24" t="b">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只在建表时定义索引的方案下成立，不代表能调整已有库索引，也不证明完整选择与调整能力。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q25" t="b">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>删除/维护索引操作不等于诊断索引问题；具体变更理由与效果核查仍未由本知识单独覆盖。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q26" t="b">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>第11页仅明示有无索引查询效果对比；K3指与其他索引知识组合的观察线索，不证明完整方案选择及迭代调整闭环。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q27" t="b">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>在已有质量检查条件的前提下，支持筛选待核查记录；不涵盖质量维度定义、规则制定、异常原因判断和完整核查结果验证。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q31" t="b">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>仅对应内外连接语法及关联条件；完整业务语义、重复行及结果正确性仍需任务情境核查。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q33" t="b">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>一般SELECT只提供表达框架，不自动支持连接条件设计或多表结果核验。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q34" t="b">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>外键知识帮助理解关联字段；连接并不要求存在外键约束</t>
+          <t>第5页外键约束知识仅在参照关系解释场景中帮助理解关联字段；JOIN本身不依赖外键定义，因此采用条件性K4而非一般基础前提。</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>外键知识仅在解释既有参照关系时提供条件性理解线索；SQL JOIN不要求已定义外键约束，不是必要前提。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="Q35" t="b">
